--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct+DICE/adaptive/entropy/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct+DICE/adaptive/entropy/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -1095,6 +1095,376 @@
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>dice_p=5,ash_p=None,react_th=1.0,scale_th=2.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.1,scale_th=2.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>96.19</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.9,scale_th=2.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>89.36</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.8,scale_th=2.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.7,scale_th=2.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>93.31</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.6,scale_th=2.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>97.01000000000001</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.8,scale_th=3.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.8,scale_th=2.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>89.67</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.8,scale_th=1.5,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>87.56999999999999</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=0.8,scale_th=2.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=0.8,scale_th=2.0,type=entropy</t>
         </is>
       </c>
     </row>
